--- a/artfynd/A 39457-2023 artfynd.xlsx
+++ b/artfynd/A 39457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129723250</v>
       </c>
       <c r="B2" t="n">
-        <v>57576</v>
+        <v>57577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39457-2023 artfynd.xlsx
+++ b/artfynd/A 39457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129723250</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
+        <v>57578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39457-2023 artfynd.xlsx
+++ b/artfynd/A 39457-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129723250</v>
       </c>
       <c r="B2" t="n">
-        <v>57578</v>
+        <v>57581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
